--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487911_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487911_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W. LEVEQUE</t>
+          <t>M. STRIKKER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.3179</v>
+        <v>9.1547</v>
       </c>
       <c r="E2" t="n">
-        <v>8.885400000000001</v>
+        <v>7.9817</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4325</v>
+        <v>1.173</v>
       </c>
       <c r="G2" t="n">
-        <v>2.5835</v>
+        <v>9.5382</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9613</v>
+        <v>8.729100000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6221</v>
+        <v>0.8091</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6491</v>
+        <v>9.9467</v>
       </c>
       <c r="K2" t="n">
-        <v>2.0311</v>
+        <v>8.7498</v>
       </c>
       <c r="L2" t="n">
-        <v>0.618</v>
+        <v>1.1969</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.4085</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0697</v>
+        <v>-0.0207</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0041</v>
+        <v>-0.3878</v>
       </c>
       <c r="P2" t="n">
-        <v>1.4568</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4568</v>
+        <v>1.6649</v>
       </c>
       <c r="S2" t="n">
-        <v>5.0476</v>
+        <v>0.8434</v>
       </c>
       <c r="T2" t="n">
-        <v>4.8388</v>
+        <v>0.9268</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2089</v>
+        <v>-0.0834</v>
       </c>
       <c r="V2" t="n">
         <v>0.23</v>
       </c>
       <c r="W2" t="n">
-        <v>1.3975</v>
+        <v>0.23</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. STRIKKER</t>
+          <t>W. LEVEQUE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>9.2378</v>
+        <v>6.509</v>
       </c>
       <c r="E3" t="n">
-        <v>7.595</v>
+        <v>6.1645</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6428</v>
+        <v>0.3444</v>
       </c>
       <c r="G3" t="n">
-        <v>9.5382</v>
+        <v>2.5835</v>
       </c>
       <c r="H3" t="n">
-        <v>8.729100000000001</v>
+        <v>1.9613</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8091</v>
+        <v>0.6221</v>
       </c>
       <c r="J3" t="n">
-        <v>9.9467</v>
+        <v>2.6491</v>
       </c>
       <c r="K3" t="n">
-        <v>8.7498</v>
+        <v>2.0311</v>
       </c>
       <c r="L3" t="n">
-        <v>1.1969</v>
+        <v>0.618</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4085</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0207</v>
+        <v>-0.0697</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3878</v>
+        <v>0.0041</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.4568</v>
+        <v>1.4568</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6649</v>
+        <v>1.4568</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9265</v>
+        <v>2.2387</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5401</v>
+        <v>2.1179</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3863</v>
+        <v>0.1208</v>
       </c>
       <c r="V3" t="n">
         <v>0.23</v>
       </c>
       <c r="W3" t="n">
-        <v>0.23</v>
+        <v>1.3975</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3971</v>
+        <v>4.4352</v>
       </c>
       <c r="E4" t="n">
-        <v>3.598</v>
+        <v>3.8123</v>
       </c>
       <c r="F4" t="n">
-        <v>0.799</v>
+        <v>0.6229</v>
       </c>
       <c r="G4" t="n">
         <v>2.1012</v>
@@ -766,13 +766,13 @@
         <v>0.8325</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1065</v>
+        <v>1.1446</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2824</v>
+        <v>0.4968</v>
       </c>
       <c r="U4" t="n">
-        <v>0.824</v>
+        <v>0.6479</v>
       </c>
       <c r="V4" t="n">
         <v>1.3975</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4493</v>
+        <v>1.0985</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3525</v>
+        <v>1.031</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0969</v>
+        <v>0.0675</v>
       </c>
       <c r="G5" t="n">
         <v>0.0621</v>
@@ -844,13 +844,13 @@
         <v>0.2081</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8253</v>
+        <v>0.4745</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4534</v>
+        <v>0.1319</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3719</v>
+        <v>0.3425</v>
       </c>
       <c r="V5" t="n">
         <v>0.3538</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. MENDES LIMA</t>
+          <t>A. MAZAIRA GOMEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9016</v>
+        <v>1.0028</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3003</v>
+        <v>1.168</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6012999999999999</v>
+        <v>-0.1652</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1486</v>
+        <v>-0.7884</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5632</v>
+        <v>-1.1534</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5854</v>
+        <v>0.3649</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8099</v>
+        <v>-0.0697</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1919</v>
+        <v>-0.1815</v>
       </c>
       <c r="L6" t="n">
-        <v>0.618</v>
+        <v>0.1118</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3387</v>
+        <v>-0.7187</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3713</v>
+        <v>-0.9719</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0326</v>
+        <v>0.2531</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6244</v>
+        <v>1.2487</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6244</v>
+        <v>1.2487</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2962</v>
+        <v>1.2502</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5096000000000001</v>
+        <v>0.7778</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8058</v>
+        <v>0.4724</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.1675</v>
+        <v>-0.7076</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.4599</v>
       </c>
       <c r="X6" t="n">
         <v>-1.1675</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. LAFUENTE SISO</t>
+          <t>P. MENDES LIMA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3625</v>
+        <v>0.9589</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4</v>
+        <v>0.6218</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0375</v>
+        <v>0.3371</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6143</v>
+        <v>1.1486</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2134</v>
+        <v>0.5632</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4009</v>
+        <v>0.5854</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0229</v>
+        <v>0.8099</v>
       </c>
       <c r="K7" t="n">
-        <v>0.285</v>
+        <v>0.1919</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.2621</v>
+        <v>0.618</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6371</v>
+        <v>0.3387</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4984</v>
+        <v>0.3713</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1388</v>
+        <v>-0.0326</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2081</v>
+        <v>0.6244</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.2487</v>
+        <v>0.6244</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0437</v>
+        <v>0.3535</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6178</v>
+        <v>-0.1881</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5741000000000001</v>
+        <v>0.5416</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. MAZAIRA GOMEZ</t>
+          <t>A. LAFUENTE SISO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6903</v>
+        <v>0.2298</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2903</v>
+        <v>-0.0133</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4001</v>
+        <v>0.243</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7884</v>
+        <v>-0.6143</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1534</v>
+        <v>-0.2134</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3649</v>
+        <v>-0.4009</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0697</v>
+        <v>0.0229</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1815</v>
+        <v>0.285</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1118</v>
+        <v>-0.2621</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7187</v>
+        <v>-0.6371</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9719</v>
+        <v>-0.4984</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2531</v>
+        <v>-0.1388</v>
       </c>
       <c r="P8" t="n">
-        <v>1.2487</v>
+        <v>0.2081</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R8" t="n">
         <v>1.2487</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.443</v>
+        <v>0.6359</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6805</v>
+        <v>1.0045</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2375</v>
+        <v>-0.3685</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.7076</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.4599</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. CAMPENY LLOVERAS</t>
+          <t>A. PALAZUELOS PEREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.421</v>
+        <v>-0.7356</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9247</v>
+        <v>-0.0185</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4962</v>
+        <v>-0.7171</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2464</v>
+        <v>-0.7103</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0062</v>
+        <v>0.8082</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2401</v>
+        <v>-1.5186</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5401</v>
+        <v>-0.4733</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0959</v>
+        <v>1.0126</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.636</v>
+        <v>-1.4859</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7063</v>
+        <v>-0.237</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1022</v>
+        <v>-0.2043</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6041</v>
+        <v>-0.0326</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4162</v>
+        <v>1.0406</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4162</v>
+        <v>1.0406</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1168</v>
+        <v>0.3316</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3229</v>
+        <v>0.4548</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2061</v>
+        <v>-0.1233</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.7076</v>
+        <v>-1.3975</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.7076</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. USAOLA REDONDO</t>
+          <t>P. CAMPENY LLOVERAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1375</v>
+        <v>-1.5765</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7618</v>
+        <v>-1.1391</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3756</v>
+        <v>-0.4375</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0969</v>
+        <v>-1.2464</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1727</v>
+        <v>-0.0062</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9242</v>
+        <v>-1.2401</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.656</v>
+        <v>-0.5401</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0192</v>
+        <v>0.0959</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6752</v>
+        <v>-0.636</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4409</v>
+        <v>-0.7063</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1919</v>
+        <v>-0.1022</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.249</v>
+        <v>-0.6041</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.0406</v>
+        <v>0.4162</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.4162</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0.0388</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.1086</v>
       </c>
       <c r="U10" t="n">
-        <v>0.06519999999999999</v>
+        <v>-0.1474</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.7076</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.7076</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. PALAZUELOS PEREZ</t>
+          <t>A. USAOLA REDONDO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2057</v>
+        <v>-2.0303</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0481</v>
+        <v>-1.6547</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1575</v>
+        <v>-0.3756</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7103</v>
+        <v>-1.0969</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8082</v>
+        <v>-0.1727</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.5186</v>
+        <v>-0.9242</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4733</v>
+        <v>-0.656</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0126</v>
+        <v>0.0192</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.4859</v>
+        <v>-0.6752</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.237</v>
+        <v>-0.4409</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2043</v>
+        <v>-0.1919</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0326</v>
+        <v>-0.249</v>
       </c>
       <c r="P11" t="n">
-        <v>1.0406</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R11" t="n">
-        <v>1.0406</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1385</v>
+        <v>0.1072</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5748</v>
+        <v>0.0419</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5637</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.3975</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.3975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.6871</v>
+        <v>-5.9205</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8536</v>
+        <v>-4.175</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8335</v>
+        <v>-1.7455</v>
       </c>
       <c r="G12" t="n">
         <v>-3.0164</v>
@@ -1390,13 +1390,13 @@
         <v>0.6244</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1494</v>
+        <v>-0.3828</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1924</v>
+        <v>-0.129</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3418</v>
+        <v>-0.2537</v>
       </c>
       <c r="V12" t="n">
         <v>-2.1051</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>12.7996</v>
+        <v>13.126</v>
       </c>
       <c r="E13" t="n">
-        <v>13.4527</v>
+        <v>13.7787</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6528999999999996</v>
+        <v>-0.6529999999999998</v>
       </c>
       <c r="G13" t="n">
         <v>7.960900000000001</v>
@@ -1447,7 +1447,7 @@
         <v>12.5761</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6734000000000008</v>
+        <v>0.6734000000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-5.2884</v>
@@ -1468,19 +1468,19 @@
         <v>9.3653</v>
       </c>
       <c r="S13" t="n">
-        <v>6.6317</v>
+        <v>6.958</v>
       </c>
       <c r="T13" t="n">
-        <v>5.417700000000001</v>
+        <v>5.7439</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2139</v>
+        <v>1.2141</v>
       </c>
       <c r="V13" t="n">
         <v>-3.874</v>
       </c>
       <c r="W13" t="n">
-        <v>2.0697</v>
+        <v>2.069699999999999</v>
       </c>
       <c r="X13" t="n">
         <v>-5.9437</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.7877</v>
+        <v>6.2868</v>
       </c>
       <c r="E14" t="n">
-        <v>9.2759</v>
+        <v>8.847300000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.4883</v>
+        <v>-2.5605</v>
       </c>
       <c r="G14" t="n">
         <v>4.2139</v>
@@ -1546,13 +1546,13 @@
         <v>1.4568</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.1151</v>
+        <v>-1.616</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1247</v>
+        <v>-0.5533</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.9904</v>
+        <v>-1.0627</v>
       </c>
       <c r="V14" t="n">
         <v>3.2726</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1342</v>
+        <v>1.3572</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3785</v>
+        <v>0.5212</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7557</v>
+        <v>0.836</v>
       </c>
       <c r="G15" t="n">
         <v>0.5573</v>
@@ -1624,13 +1624,13 @@
         <v>0.2081</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8912</v>
+        <v>0.1142</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9068000000000001</v>
+        <v>0.0496</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0156</v>
+        <v>0.0646</v>
       </c>
       <c r="V15" t="n">
         <v>0.4776</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MENENDEZ GARCIA</t>
+          <t>M. OKAFOR AUGUSTIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5789</v>
+        <v>0.3541</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4832</v>
+        <v>1.5109</v>
       </c>
       <c r="F16" t="n">
-        <v>0.09569999999999999</v>
+        <v>-1.1568</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.0642</v>
+        <v>1.0985</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.8699</v>
+        <v>-0.0788</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1943</v>
+        <v>1.1773</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.1125</v>
+        <v>1.8295</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.2693</v>
+        <v>1.0849</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1568</v>
+        <v>0.7446</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.9517</v>
+        <v>-0.731</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.6007</v>
+        <v>-1.1637</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.351</v>
+        <v>0.4327</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0.8325</v>
       </c>
       <c r="S16" t="n">
-        <v>3.4943</v>
+        <v>-0.9931</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2794</v>
+        <v>-0.3186</v>
       </c>
       <c r="U16" t="n">
-        <v>1.2149</v>
+        <v>-0.6745</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3975</v>
+        <v>-0.5838</v>
       </c>
       <c r="W16" t="n">
-        <v>1.3975</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. OKAFOR AUGUSTIN</t>
+          <t>J. REILLY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0222</v>
+        <v>-0.8961</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1894</v>
+        <v>0.4045</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2116</v>
+        <v>-1.3006</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0985</v>
+        <v>0.3705</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0788</v>
+        <v>0.2391</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1773</v>
+        <v>0.1314</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8295</v>
+        <v>1.526</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0849</v>
+        <v>1.1129</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7446</v>
+        <v>0.4131</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.731</v>
+        <v>-1.1555</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1637</v>
+        <v>-0.8738</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4327</v>
+        <v>-0.2817</v>
       </c>
       <c r="P17" t="n">
-        <v>0.8325</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R17" t="n">
-        <v>0.8325</v>
+        <v>0.6244</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3694</v>
+        <v>-0.6204</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.64</v>
+        <v>-0.0809</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7292999999999999</v>
+        <v>-0.5395</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5838</v>
+        <v>-0.23</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5838</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. REILLY</t>
+          <t>S. BARROS GARCIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.7906</v>
+        <v>-1.8746</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0241</v>
+        <v>0.7195</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7664</v>
+        <v>-2.594</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3705</v>
+        <v>-0.1078</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2391</v>
+        <v>0.8531</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1314</v>
+        <v>-0.9609</v>
       </c>
       <c r="J18" t="n">
-        <v>1.526</v>
+        <v>2.2112</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1129</v>
+        <v>3.0701</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4131</v>
+        <v>-0.8589</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1555</v>
+        <v>-2.319</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8738</v>
+        <v>-2.217</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2817</v>
+        <v>-0.102</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.4162</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6244</v>
+        <v>1.2487</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.5149</v>
+        <v>-0.9343</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.5780999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0053</v>
+        <v>-0.3562</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.23</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. BARROS GARCIA</t>
+          <t>J. MENENDEZ GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.9882</v>
+        <v>-1.9719</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1378</v>
+        <v>-1.1242</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.8504</v>
+        <v>-0.8477</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1078</v>
+        <v>-3.0642</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8531</v>
+        <v>-2.8699</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9609</v>
+        <v>-0.1943</v>
       </c>
       <c r="J19" t="n">
-        <v>2.2112</v>
+        <v>-1.1125</v>
       </c>
       <c r="K19" t="n">
-        <v>3.0701</v>
+        <v>-1.2693</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.8589</v>
+        <v>0.1568</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.319</v>
+        <v>-1.9517</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.217</v>
+        <v>-1.6007</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.102</v>
+        <v>-0.351</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.8325</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q19" t="n">
         <v>-2.0812</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2487</v>
+        <v>0.8325</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.0479</v>
+        <v>0.9436</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.4354</v>
+        <v>0.6721</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6125</v>
+        <v>0.2715</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.3975</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1675</v>
+        <v>1.3975</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.247</v>
+        <v>-3.4382</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.3523</v>
+        <v>-3.6022</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1053</v>
+        <v>0.164</v>
       </c>
       <c r="G20" t="n">
         <v>-4.3942</v>
@@ -2014,13 +2014,13 @@
         <v>0.2081</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7685</v>
+        <v>0.0403</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8482</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0796</v>
+        <v>0.1383</v>
       </c>
       <c r="V20" t="n">
         <v>0.7076</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. DUKE TOUSSAINT</t>
+          <t>G. ARCOS GONZALEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.4311</v>
+        <v>-5.0174</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4143</v>
+        <v>-3.7812</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.0168</v>
+        <v>-1.2362</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.2827</v>
+        <v>-3.3521</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.766</v>
+        <v>-1.2662</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5168</v>
+        <v>-2.086</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.4048</v>
+        <v>-1.4372</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.5615</v>
+        <v>0.0487</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1568</v>
+        <v>-1.4859</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.878</v>
+        <v>-1.915</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2044</v>
+        <v>-1.3149</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6735</v>
+        <v>-0.6001</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4162</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6244</v>
+        <v>1.2487</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2108</v>
+        <v>-1.1866</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3849</v>
+        <v>-0.2628</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5956</v>
+        <v>-0.9237</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.5213</v>
+        <v>0.3538</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3538</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1675</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. ARCOS GONZALEZ</t>
+          <t>I. DUKE TOUSSAINT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.8214</v>
+        <v>-5.4565</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.7456</v>
+        <v>-2.8429</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0758</v>
+        <v>-2.6136</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.3521</v>
+        <v>-3.2827</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2662</v>
+        <v>-2.766</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.086</v>
+        <v>-0.5168</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.4372</v>
+        <v>-1.4048</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0487</v>
+        <v>-1.5615</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.4859</v>
+        <v>0.1568</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.915</v>
+        <v>-1.878</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3149</v>
+        <v>-1.2044</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6001</v>
+        <v>-0.6735</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.8325</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2487</v>
+        <v>0.6244</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.9906</v>
+        <v>-0.2362</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2272</v>
+        <v>-0.0438</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.7634</v>
+        <v>-0.1924</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3538</v>
+        <v>-1.5213</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.3538</v>
       </c>
       <c r="X22" t="n">
-        <v>0.3538</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-12.7997</v>
+        <v>-10.6566</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6529000000000025</v>
+        <v>0.6529000000000007</v>
       </c>
       <c r="F23" t="n">
-        <v>-13.4526</v>
+        <v>-11.3094</v>
       </c>
       <c r="G23" t="n">
         <v>-7.960800000000001</v>
@@ -2221,13 +2221,13 @@
         <v>1.612399999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>5.2885</v>
+        <v>5.288500000000002</v>
       </c>
       <c r="K23" t="n">
         <v>3.0025</v>
       </c>
       <c r="L23" t="n">
-        <v>2.286099999999999</v>
+        <v>2.2861</v>
       </c>
       <c r="M23" t="n">
         <v>-13.2494</v>
@@ -2236,28 +2236,28 @@
         <v>-12.5759</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6734</v>
+        <v>-0.6733999999999999</v>
       </c>
       <c r="P23" t="n">
         <v>-2.0812</v>
       </c>
       <c r="Q23" t="n">
-        <v>-9.365400000000001</v>
+        <v>-9.365399999999999</v>
       </c>
       <c r="R23" t="n">
         <v>7.2842</v>
       </c>
       <c r="S23" t="n">
-        <v>-6.631699999999999</v>
+        <v>-4.4885</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.214</v>
+        <v>-1.2139</v>
       </c>
       <c r="U23" t="n">
-        <v>-5.417599999999999</v>
+        <v>-3.2746</v>
       </c>
       <c r="V23" t="n">
-        <v>3.874</v>
+        <v>3.874000000000001</v>
       </c>
       <c r="W23" t="n">
         <v>5.9437</v>
